--- a/doc_testbed/Cape25d_pre-deployment-tests.xlsx
+++ b/doc_testbed/Cape25d_pre-deployment-tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hans\Documents\GitHub\shepherd_v2_planning\doc_testbed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D262C28E-FB0C-4372-9605-237C071DB862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4A7C40-89C8-4ADF-B1A4-A00079795A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5964" yWindow="6060" windowWidth="21288" windowHeight="18900" xr2:uid="{0961F1A4-98B1-4F35-911A-F9CB780BF838}"/>
+    <workbookView xWindow="14592" yWindow="6048" windowWidth="20208" windowHeight="18600" xr2:uid="{0961F1A4-98B1-4F35-911A-F9CB780BF838}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>Target</t>
   </si>
@@ -82,6 +82,103 @@
   </si>
   <si>
     <t>PI5</t>
+  </si>
+  <si>
+    <t>25d01</t>
+  </si>
+  <si>
+    <t>25d02</t>
+  </si>
+  <si>
+    <t>25d03</t>
+  </si>
+  <si>
+    <t>25d04</t>
+  </si>
+  <si>
+    <t>25d05</t>
+  </si>
+  <si>
+    <t>25d06</t>
+  </si>
+  <si>
+    <t>25d07</t>
+  </si>
+  <si>
+    <t>25d08</t>
+  </si>
+  <si>
+    <t>25d09</t>
+  </si>
+  <si>
+    <t>25d10</t>
+  </si>
+  <si>
+    <t>25d11</t>
+  </si>
+  <si>
+    <t>25d12</t>
+  </si>
+  <si>
+    <t>25d13</t>
+  </si>
+  <si>
+    <t>25d14</t>
+  </si>
+  <si>
+    <t>25d15</t>
+  </si>
+  <si>
+    <t>25d16</t>
+  </si>
+  <si>
+    <t>25d17</t>
+  </si>
+  <si>
+    <t>25d18</t>
+  </si>
+  <si>
+    <t>25d19</t>
+  </si>
+  <si>
+    <t>25d20</t>
+  </si>
+  <si>
+    <t>25d21</t>
+  </si>
+  <si>
+    <t>25d22</t>
+  </si>
+  <si>
+    <t>25d23</t>
+  </si>
+  <si>
+    <t>25d24</t>
+  </si>
+  <si>
+    <t>25d25</t>
+  </si>
+  <si>
+    <t>25d26</t>
+  </si>
+  <si>
+    <t>25d27</t>
+  </si>
+  <si>
+    <t>25d28</t>
+  </si>
+  <si>
+    <t>25d29</t>
+  </si>
+  <si>
+    <t>25d30</t>
+  </si>
+  <si>
+    <t>crossed resistors partially fixed, 
+U5 (main PwrReg) missing</t>
+  </si>
+  <si>
+    <t>label reads v2.5c (for all)</t>
   </si>
 </sst>
 </file>
@@ -139,17 +236,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -160,51 +302,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -230,22 +327,22 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AD7FE81-A7F6-4917-AEFC-78F3D59AF956}" name="Table1" displayName="Table1" ref="A1:P31" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A1:P31" xr:uid="{3AD7FE81-A7F6-4917-AEFC-78F3D59AF956}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{AB1111EA-1189-4670-B60E-2E04180241E7}" name="Target" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{9C88A57E-F780-4CC3-BA99-046F311B4956}" name="Visual" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{7195CB4D-4AF3-465C-AF5A-354CCBF97D0C}" name="C_Off" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{2CC13D68-4199-4EB2-B005-409CEE8AEA08}" name="C_On" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{903CC865-8B03-4D80-A86B-E4E0A53B7DB0}" name="Mod_Emu" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{4B5E2432-0988-4E75-864C-D73D05146064}" name="Mod_Gpio" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{94650C81-E1B2-4E5C-8E32-27458281274E}" name="Add_Caps" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{4F9009E0-8056-4545-95BD-48D33DC9717D}" name="Add_Hdr" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{1D628D7A-B725-444C-A77B-0CA23F68FD1C}" name="Cleaned" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{383AAC32-63FB-4BEC-BCC1-92C187B19C3C}" name="Tests" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{126B0F9E-2DEB-4F91-8378-718C5F0ADC82}" name="Cal_Emu" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{4BB433E8-BB2C-434A-86F8-CAD847215D39}" name="Dplm_Bbone" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{FF2AF165-23D6-4020-80AF-07BF1E63D03B}" name="Dplm_Target" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{5B80B321-6B6C-41B8-AE7E-C24D9A411E6E}" name="Dplm_Room" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{B0B7780B-D915-49CD-86B4-61AE16185936}" name="Dplm_Socket" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{9C254D40-B1FA-4933-8C96-05EFD55C114C}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{AB1111EA-1189-4670-B60E-2E04180241E7}" name="Target" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{9C88A57E-F780-4CC3-BA99-046F311B4956}" name="Visual" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{7195CB4D-4AF3-465C-AF5A-354CCBF97D0C}" name="C_Off" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{2CC13D68-4199-4EB2-B005-409CEE8AEA08}" name="C_On" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{903CC865-8B03-4D80-A86B-E4E0A53B7DB0}" name="Mod_Emu" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{4B5E2432-0988-4E75-864C-D73D05146064}" name="Mod_Gpio" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{94650C81-E1B2-4E5C-8E32-27458281274E}" name="Add_Caps" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{4F9009E0-8056-4545-95BD-48D33DC9717D}" name="Add_Hdr" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{1D628D7A-B725-444C-A77B-0CA23F68FD1C}" name="Cleaned" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{383AAC32-63FB-4BEC-BCC1-92C187B19C3C}" name="Tests" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{126B0F9E-2DEB-4F91-8378-718C5F0ADC82}" name="Cal_Emu" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{4BB433E8-BB2C-434A-86F8-CAD847215D39}" name="Dplm_Bbone" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{FF2AF165-23D6-4020-80AF-07BF1E63D03B}" name="Dplm_Target" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{5B80B321-6B6C-41B8-AE7E-C24D9A411E6E}" name="Dplm_Room" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{B0B7780B-D915-49CD-86B4-61AE16185936}" name="Dplm_Socket" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{9C254D40-B1FA-4933-8C96-05EFD55C114C}" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -613,8 +710,8 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>2401</v>
+      <c r="A2" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -637,8 +734,8 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>2402</v>
+      <c r="A3" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>18</v>
@@ -661,32 +758,32 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>2403</v>
+      <c r="A4" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
       <c r="P4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>2404</v>
+      <c r="A5" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
@@ -704,11 +801,13 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
+      <c r="P5" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>2405</v>
+      <c r="A6" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -724,11 +823,13 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>2406</v>
+      <c r="A7" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -747,8 +848,8 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>2407</v>
+      <c r="A8" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -767,8 +868,8 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>2408</v>
+      <c r="A9" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -787,8 +888,8 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>2409</v>
+      <c r="A10" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -807,8 +908,8 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>2410</v>
+      <c r="A11" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -827,8 +928,8 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>2411</v>
+      <c r="A12" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -847,8 +948,8 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>2412</v>
+      <c r="A13" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -867,8 +968,8 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>2413</v>
+      <c r="A14" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -887,8 +988,8 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>2414</v>
+      <c r="A15" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -907,8 +1008,8 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>2415</v>
+      <c r="A16" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -927,8 +1028,8 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>2416</v>
+      <c r="A17" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -947,8 +1048,8 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>2417</v>
+      <c r="A18" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -967,8 +1068,8 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>2418</v>
+      <c r="A19" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -987,8 +1088,8 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>2419</v>
+      <c r="A20" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1007,8 +1108,8 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>2420</v>
+      <c r="A21" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1027,8 +1128,8 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>2421</v>
+      <c r="A22" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1047,8 +1148,8 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>2422</v>
+      <c r="A23" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1067,8 +1168,8 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>2423</v>
+      <c r="A24" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1087,8 +1188,8 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>2424</v>
+      <c r="A25" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1107,8 +1208,8 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>2425</v>
+      <c r="A26" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1127,8 +1228,8 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>2426</v>
+      <c r="A27" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1147,8 +1248,8 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>2427</v>
+      <c r="A28" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1167,8 +1268,8 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>2428</v>
+      <c r="A29" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1187,8 +1288,8 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <v>2429</v>
+      <c r="A30" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1207,8 +1308,8 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <v>2430</v>
+      <c r="A31" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
